--- a/Slot-2.xlsx
+++ b/Slot-2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Narayani\TechAlfha\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/270dcdb5046aa350/Desktop/CyberHunt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C767322C-4C2A-4D29-8093-D0D60FC90ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{C767322C-4C2A-4D29-8093-D0D60FC90ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFD6101A-BC1A-4CBA-9A54-E3D5387939AC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{05538C94-7507-4DB1-A276-DCBA3B8A7322}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{05538C94-7507-4DB1-A276-DCBA3B8A7322}"/>
   </bookViews>
   <sheets>
     <sheet name="B" sheetId="1" r:id="rId1"/>
@@ -622,7 +622,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -638,6 +638,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -661,9 +664,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -701,7 +704,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -807,7 +810,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -949,7 +952,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -997,7 +1000,7 @@
       <c r="D2" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="7" t="s">
         <v>153</v>
       </c>
     </row>
@@ -1688,6 +1691,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E31" r:id="rId1" xr:uid="{8378BD0F-CC6B-4D59-AE5E-5D4F7A4D90B9}"/>
+    <hyperlink ref="E2" r:id="rId2" xr:uid="{B8B2737B-6AEC-4DAE-84CF-86C2E599FF15}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Slot-2.xlsx
+++ b/Slot-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/270dcdb5046aa350/Desktop/CyberHunt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{C767322C-4C2A-4D29-8093-D0D60FC90ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFD6101A-BC1A-4CBA-9A54-E3D5387939AC}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{C767322C-4C2A-4D29-8093-D0D60FC90ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4590F53-4B87-4120-ABFB-E69F3B5F3332}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{05538C94-7507-4DB1-A276-DCBA3B8A7322}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{05538C94-7507-4DB1-A276-DCBA3B8A7322}"/>
   </bookViews>
   <sheets>
     <sheet name="B" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="163">
   <si>
     <t>pranitabharathi22.c@gmail.com</t>
   </si>
@@ -520,6 +520,9 @@
   </si>
   <si>
     <t>Sr.No</t>
+  </si>
+  <si>
+    <t>https://meet.google.com/xuh-qmwt-ymz</t>
   </si>
 </sst>
 </file>
@@ -622,7 +625,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -643,6 +646,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -960,7 +964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D6F40FF-4E9B-445B-BF2A-D939AC6B3BDA}">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" customWidth="1"/>
@@ -968,9 +972,10 @@
     <col min="3" max="3" width="38.77734375" customWidth="1"/>
     <col min="4" max="4" width="26.5546875" customWidth="1"/>
     <col min="5" max="5" width="46.88671875" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>161</v>
       </c>
@@ -987,7 +992,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1003,8 +1008,11 @@
       <c r="E2" s="7" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F2" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1017,11 +1025,14 @@
       <c r="D3" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="7" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F3" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1037,8 +1048,11 @@
       <c r="E4" s="3" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F4" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1054,8 +1068,11 @@
       <c r="E5" s="3" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F5" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1071,8 +1088,11 @@
       <c r="E6" s="3" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F6" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1088,8 +1108,11 @@
       <c r="E7" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F7" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1105,8 +1128,11 @@
       <c r="E8" s="3" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F8" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1122,8 +1148,11 @@
       <c r="E9" s="3" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F9" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1139,8 +1168,11 @@
       <c r="E10" s="3" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F10" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1156,8 +1188,11 @@
       <c r="E11" s="3" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F11" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -1173,8 +1208,11 @@
       <c r="E12" s="3" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F12" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1190,8 +1228,11 @@
       <c r="E13" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F13" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1207,8 +1248,11 @@
       <c r="E14" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F14" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1224,8 +1268,11 @@
       <c r="E15" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F15" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1241,8 +1288,11 @@
       <c r="E16" s="3" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F16" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -1258,8 +1308,11 @@
       <c r="E17" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F17" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1275,8 +1328,11 @@
       <c r="E18" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F18" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1292,8 +1348,11 @@
       <c r="E19" s="3" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F19" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1309,8 +1368,11 @@
       <c r="E20" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F20" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -1326,8 +1388,11 @@
       <c r="E21" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F21" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -1343,8 +1408,11 @@
       <c r="E22" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F22" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -1360,8 +1428,11 @@
       <c r="E23" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F23" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -1377,8 +1448,11 @@
       <c r="E24" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F24" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -1394,8 +1468,11 @@
       <c r="E25" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F25" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -1411,8 +1488,11 @@
       <c r="E26" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F26" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -1428,8 +1508,11 @@
       <c r="E27" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F27" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -1445,8 +1528,11 @@
       <c r="E28" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F28" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -1462,8 +1548,11 @@
       <c r="E29" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F29" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -1479,8 +1568,11 @@
       <c r="E30" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F30" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -1494,8 +1586,11 @@
       <c r="E31" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F31" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -1509,8 +1604,11 @@
       <c r="E32" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F32" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -1524,8 +1622,11 @@
       <c r="E33" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F33" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -1539,8 +1640,11 @@
       <c r="E34" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F34" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -1554,8 +1658,11 @@
       <c r="E35" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F35" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -1569,8 +1676,11 @@
       <c r="E36" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F36" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -1584,8 +1694,11 @@
       <c r="E37" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F37" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -1599,8 +1712,11 @@
       <c r="E38" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F38" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -1614,8 +1730,11 @@
       <c r="E39" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F39" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -1629,8 +1748,11 @@
       <c r="E40" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F40" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -1644,8 +1766,11 @@
       <c r="E41" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F41" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -1657,8 +1782,11 @@
         <v>6</v>
       </c>
       <c r="E42" s="1"/>
-    </row>
-    <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F42" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -1672,8 +1800,11 @@
       <c r="E43" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F43" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -1686,13 +1817,20 @@
       </c>
       <c r="E44" s="1" t="s">
         <v>0</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E31" r:id="rId1" xr:uid="{8378BD0F-CC6B-4D59-AE5E-5D4F7A4D90B9}"/>
     <hyperlink ref="E2" r:id="rId2" xr:uid="{B8B2737B-6AEC-4DAE-84CF-86C2E599FF15}"/>
+    <hyperlink ref="E3" r:id="rId3" xr:uid="{9046401F-2AB5-456F-B5AD-406C92DCBCC6}"/>
+    <hyperlink ref="F2" r:id="rId4" xr:uid="{0616A881-3073-4A5C-A288-97145BAE84C9}"/>
+    <hyperlink ref="F3:F44" r:id="rId5" display="https://meet.google.com/xuh-qmwt-ymz" xr:uid="{5EEB0B27-CD81-441D-BE09-29A0EDE36AC1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/Slot-2.xlsx
+++ b/Slot-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/270dcdb5046aa350/Desktop/CyberHunt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{C767322C-4C2A-4D29-8093-D0D60FC90ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4590F53-4B87-4120-ABFB-E69F3B5F3332}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{C767322C-4C2A-4D29-8093-D0D60FC90ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{740FDD30-BB34-4F50-AC20-7A1473E5EA62}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{05538C94-7507-4DB1-A276-DCBA3B8A7322}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{05538C94-7507-4DB1-A276-DCBA3B8A7322}"/>
   </bookViews>
   <sheets>
     <sheet name="B" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="164">
   <si>
     <t>pranitabharathi22.c@gmail.com</t>
   </si>
@@ -523,6 +523,9 @@
   </si>
   <si>
     <t>https://meet.google.com/xuh-qmwt-ymz</t>
+  </si>
+  <si>
+    <t>vairagadeshravani@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -665,6 +668,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1781,7 +1788,9 @@
       <c r="D42" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E42" s="1"/>
+      <c r="E42" s="1" t="s">
+        <v>163</v>
+      </c>
       <c r="F42" s="8" t="s">
         <v>162</v>
       </c>

--- a/Slot-2.xlsx
+++ b/Slot-2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/270dcdb5046aa350/Desktop/CyberHunt/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/270dcdb5046aa350/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{C767322C-4C2A-4D29-8093-D0D60FC90ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{740FDD30-BB34-4F50-AC20-7A1473E5EA62}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FF7029D-BA81-459C-B46A-DA03FDC9B201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{05538C94-7507-4DB1-A276-DCBA3B8A7322}"/>
   </bookViews>
